--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2901c1f617d241d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8626fd20e7854466"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8626fd20e7854466"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0efba22818d44bed"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0efba22818d44bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R581fb4ce088a4f9a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R581fb4ce088a4f9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf637c7b405324e2a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf637c7b405324e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2fd4cb511f34fad"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2fd4cb511f34fad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8a85f166b2c5453f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8a85f166b2c5453f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcb3eb2b36a92467c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcb3eb2b36a92467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd81580b5d75549a4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd81580b5d75549a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b801c9053f04fe5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b801c9053f04fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra128fb8bd7034518"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra128fb8bd7034518"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcfe00ee2c54c4437"/>
   </x:sheets>
 </x:workbook>
 </file>
